--- a/Data/Trends.xlsx
+++ b/Data/Trends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupecgi-my.sharepoint.com/personal/ali_mahjoub_cgi_com/Documents/Documents/UiPath/AI Social Media Manager/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{FC83683F-42BF-4097-A0B3-C26A2A443609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08CCEAE0-71E8-441E-A8C2-EC4F7C3C5AD3}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{FC83683F-42BF-4097-A0B3-C26A2A443609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28305F6E-3194-48A0-8E46-F4BBB7E0471C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{680B1045-F99F-49B7-AF7E-A924B2A05251}"/>
   </bookViews>
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -714,7 +714,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>

--- a/Data/Trends.xlsx
+++ b/Data/Trends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupecgi-my.sharepoint.com/personal/ali_mahjoub_cgi_com/Documents/Documents/UiPath/AI Social Media Manager/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{FC83683F-42BF-4097-A0B3-C26A2A443609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28305F6E-3194-48A0-8E46-F4BBB7E0471C}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{FC83683F-42BF-4097-A0B3-C26A2A443609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF7B622-77A0-4888-A26F-227F0BD82ABC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{680B1045-F99F-49B7-AF7E-A924B2A05251}"/>
+    <workbookView xWindow="4728" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{680B1045-F99F-49B7-AF7E-A924B2A05251}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Title</t>
   </si>
@@ -66,97 +66,6 @@
   </si>
   <si>
     <t>https://broadcast.listennotes.com/the-boring-technology-behind-listen-notes-56697c2e347b</t>
-  </si>
-  <si>
-    <t>How Technology Hijacks People’s Minds</t>
-  </si>
-  <si>
-    <t>lxm</t>
-  </si>
-  <si>
-    <t>https://medium.com/@tristanharris/how-technology-hijacks-peoples-minds-from-a-magician-and-google-s-design-ethicist-56d62ef5edf3</t>
-  </si>
-  <si>
-    <t>Extremely disillusioned with technology. Please help</t>
-  </si>
-  <si>
-    <t>throwaway839246</t>
-  </si>
-  <si>
-    <t>https://gist.github.com/mGBUfLn9/7cadffcf7c3c23b7376350165a67735f</t>
-  </si>
-  <si>
-    <t>Choose Boring Technology</t>
-  </si>
-  <si>
-    <t>luu</t>
-  </si>
-  <si>
-    <t>http://boringtechnology.club/</t>
-  </si>
-  <si>
-    <t>I help seniors with technology issues</t>
-  </si>
-  <si>
-    <t>thinkingemote</t>
-  </si>
-  <si>
-    <t>https://twitter.com/_danilo/status/1583169632516509697</t>
-  </si>
-  <si>
-    <t>We at $Famous_company switched to $Hyped_technology</t>
-  </si>
-  <si>
-    <t>gok</t>
-  </si>
-  <si>
-    <t>https://saagarjha.com/blog/2020/05/10/why-we-at-famous-company-switched-to-hyped-technology/</t>
-  </si>
-  <si>
-    <t>An Open Letter Against Apple's Privacy-Invasive Content Scanning Technology</t>
-  </si>
-  <si>
-    <t>nomoretime</t>
-  </si>
-  <si>
-    <t>https://appleprivacyletter.com/</t>
-  </si>
-  <si>
-    <t>Carbon Removal Technologies</t>
-  </si>
-  <si>
-    <t>sama</t>
-  </si>
-  <si>
-    <t>http://carbon.ycombinator.com</t>
-  </si>
-  <si>
-    <t>Ask HN: What startup/technology is on your 'to watch' list?</t>
-  </si>
-  <si>
-    <t>For me a couple of interesting technology products that help me in my day-to-day job&lt;p&gt;1. Hasura
-2. Strapi
-3. Forest Admin (super interesting although I cannot ever get it to connect to a hasura backend on Heroku ¯\_(ツ)_&amp;#x2F;¯
-4. Integromat
-5. Appgyver&lt;p&gt;There are many others that I have my eye on such as NodeRed[6], but have yet to use. I do realise that these are all low-code related, however, I would be super interested in being made aware of cool other cool &amp;amp; upcoming tech that is making waves.&lt;p&gt;What&amp;#x27;s on your &amp;#x27;to watch&amp;#x27; list?&lt;p&gt;[1]&lt;a href="https:&amp;#x2F;&amp;#x2F;hasura.io&amp;#x2F;" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;hasura.io&amp;#x2F;&lt;/a&gt;&lt;p&gt;[2]&lt;a href="https:&amp;#x2F;&amp;#x2F;strapi.io&amp;#x2F;" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;strapi.io&amp;#x2F;&lt;/a&gt;&lt;p&gt;[3]&lt;a href="https:&amp;#x2F;&amp;#x2F;www.forestadmin.com&amp;#x2F;" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;www.forestadmin.com&amp;#x2F;&lt;/a&gt;&lt;p&gt;[4]&lt;a href="https:&amp;#x2F;&amp;#x2F;www.appgyver.com&amp;#x2F;" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;www.appgyver.com&amp;#x2F;&lt;/a&gt;&lt;p&gt;[5]&lt;a href="https:&amp;#x2F;&amp;#x2F;www.integromat.com&amp;#x2F;en" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;www.integromat.com&amp;#x2F;en&lt;/a&gt;&lt;p&gt;[6]&lt;a href="https:&amp;#x2F;&amp;#x2F;nodered.org&amp;#x2F;" rel="nofollow"&gt;https:&amp;#x2F;&amp;#x2F;nodered.org&amp;#x2F;&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>iameoghan</t>
-  </si>
-  <si>
-    <t>https://news.ycombinator.com/item?id=23276456</t>
-  </si>
-  <si>
-    <t>Ask HN: What are some good technology blogs to follow?</t>
-  </si>
-  <si>
-    <t>I check hacker news daily. Is there any other blogs which provides good technology content daily basis ?</t>
-  </si>
-  <si>
-    <t>buddies2705</t>
-  </si>
-  <si>
-    <t>https://news.ycombinator.com/item?id=13849430</t>
   </si>
 </sst>
 </file>
@@ -549,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E507650B-B3EB-4C59-AF85-2D736335B9CE}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
@@ -595,164 +504,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>1612</v>
-      </c>
-      <c r="E3">
-        <v>427</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>1527</v>
-      </c>
-      <c r="E4">
-        <v>714</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>1357</v>
-      </c>
-      <c r="E5">
-        <v>344</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>1276</v>
-      </c>
-      <c r="E6">
-        <v>811</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1224</v>
-      </c>
-      <c r="E7">
-        <v>200</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>1187</v>
-      </c>
-      <c r="E8">
-        <v>670</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>1187</v>
-      </c>
-      <c r="E9">
-        <v>660</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>1006</v>
-      </c>
-      <c r="E10">
-        <v>669</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11">
-        <v>893</v>
-      </c>
-      <c r="E11">
-        <v>187</v>
-      </c>
-      <c r="F11" t="s">
-        <v>37</v>
-      </c>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
